--- a/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
+++ b/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="47.300000000000004"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="35.2"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="5.5"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -169,7 +169,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>
@@ -449,12 +449,12 @@
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November 14, 2026</t>
+          <t>Sunday, November 15, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>16:30 EST</t>
+          <t>12:30 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Hamilton Metz Field - Field 1</t>
+          <t>Bush Terminal Piers Park - Soccer 03 (Back field)</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
+++ b/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
@@ -74,7 +74,7 @@
     <col min="2" max="2" bestFit="1" customWidth="1" width="28.6"/>
     <col min="3" max="3" bestFit="1" customWidth="1" width="13.200000000000001"/>
     <col min="4" max="4" bestFit="1" customWidth="1" width="47.300000000000004"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" width="6.6000000000000005"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" width="8.8"/>
     <col min="6" max="6" bestFit="1" customWidth="1" width="47.300000000000004"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="35.2"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
@@ -194,7 +194,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 - 0</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
+++ b/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
@@ -259,7 +259,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
+++ b/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 3</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
+++ b/data/2026/cjsl/fall/dynamo-soccer-club-2014.xlsx
@@ -329,7 +329,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 - 0</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
